--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU10/HRM/pre LAM_HRM-2031-0240/Panel 02/Coupon front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU10_Coupon_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU10/HRM/pre LAM_HRM-2031-0240/Panel 02/Coupon front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU10_Coupon_Front_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.79382</v>
+        <v>17.9113</v>
       </c>
       <c r="D2" t="n">
-        <v>17.48137</v>
+        <v>17.33879</v>
       </c>
       <c r="E2" t="n">
-        <v>17.69864</v>
+        <v>17.44571</v>
       </c>
       <c r="F2" t="n">
-        <v>44.22134</v>
+        <v>44.45073</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0527</v>
+        <v>0.05311</v>
       </c>
       <c r="H2" t="n">
-        <v>1.91365</v>
+        <v>1.89739</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.48188</v>
+        <v>17.65269</v>
       </c>
       <c r="D3" t="n">
-        <v>17.29877</v>
+        <v>17.16606</v>
       </c>
       <c r="E3" t="n">
-        <v>17.68167</v>
+        <v>17.25658</v>
       </c>
       <c r="F3" t="n">
-        <v>44.28732</v>
+        <v>43.66796</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05335</v>
+        <v>0.05267</v>
       </c>
       <c r="H3" t="n">
-        <v>1.92484</v>
+        <v>1.9245</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.73242</v>
+        <v>17.67915</v>
       </c>
       <c r="D4" t="n">
-        <v>16.95425</v>
+        <v>17.01629</v>
       </c>
       <c r="E4" t="n">
-        <v>17.67182</v>
+        <v>17.42499</v>
       </c>
       <c r="F4" t="n">
-        <v>44.55163</v>
+        <v>44.76278</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05298</v>
+        <v>0.05307</v>
       </c>
       <c r="H4" t="n">
-        <v>1.90498</v>
+        <v>1.88663</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17.65211</v>
+        <v>17.18758</v>
       </c>
       <c r="D6" t="n">
-        <v>16.72404</v>
+        <v>16.52636</v>
       </c>
       <c r="E6" t="n">
-        <v>17.37627</v>
+        <v>17.09878</v>
       </c>
       <c r="F6" t="n">
-        <v>22.7743</v>
+        <v>22.73575</v>
       </c>
       <c r="G6" t="n">
-        <v>35.85912</v>
+        <v>35.38861</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17.51062</v>
+        <v>17.17245</v>
       </c>
       <c r="D7" t="n">
-        <v>16.69595</v>
+        <v>16.53411</v>
       </c>
       <c r="E7" t="n">
-        <v>17.58079</v>
+        <v>16.89796</v>
       </c>
       <c r="F7" t="n">
-        <v>23.23807</v>
+        <v>22.70519</v>
       </c>
       <c r="G7" t="n">
-        <v>36.66115</v>
+        <v>35.89407</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.3027</v>
+        <v>17.7168</v>
       </c>
       <c r="D8" t="n">
-        <v>16.6605</v>
+        <v>16.92617</v>
       </c>
       <c r="E8" t="n">
-        <v>17.0742</v>
+        <v>17.49449</v>
       </c>
       <c r="F8" t="n">
-        <v>22.67842</v>
+        <v>22.66777</v>
       </c>
       <c r="G8" t="n">
-        <v>35.33417</v>
+        <v>35.7897</v>
       </c>
     </row>
     <row r="9">
@@ -650,10 +650,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.62565</v>
+        <v>0.64685</v>
       </c>
       <c r="D10" t="n">
-        <v>1.168</v>
+        <v>1.15998</v>
       </c>
     </row>
     <row r="11">
@@ -663,10 +663,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.64195</v>
+        <v>0.62579</v>
       </c>
       <c r="D11" t="n">
-        <v>1.17192</v>
+        <v>1.17128</v>
       </c>
     </row>
     <row r="12">
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.63183</v>
+        <v>0.63776</v>
       </c>
       <c r="D12" t="n">
-        <v>1.18163</v>
+        <v>1.16497</v>
       </c>
     </row>
   </sheetData>
